--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>509.2914611878929</v>
+        <v>509.3042878069216</v>
       </c>
       <c r="C2">
-        <v>355.3664490273147</v>
+        <v>353.9906575053664</v>
       </c>
       <c r="D2">
-        <v>304.585563168679</v>
+        <v>303.8404812546415</v>
       </c>
       <c r="E2">
-        <v>280.1723854596625</v>
+        <v>280.0796850804858</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>598.4954603342391</v>
+        <v>598.5000487709179</v>
       </c>
       <c r="C3">
-        <v>418.9857197695598</v>
+        <v>417.3265032848843</v>
       </c>
       <c r="D3">
-        <v>357.3558453484139</v>
+        <v>356.4764936245912</v>
       </c>
       <c r="E3">
-        <v>331.5657373738654</v>
+        <v>331.4544765245645</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>572.6393071452801</v>
+        <v>572.6367821519409</v>
       </c>
       <c r="C4">
-        <v>402.1265504482544</v>
+        <v>400.5449677611053</v>
       </c>
       <c r="D4">
-        <v>343.989179217273</v>
+        <v>343.1516055476719</v>
       </c>
       <c r="E4">
-        <v>319.5669083563945</v>
+        <v>319.4578435016544</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>393.4905759255767</v>
+        <v>393.4910095147469</v>
       </c>
       <c r="C5">
-        <v>276.213026956218</v>
+        <v>275.0986261890758</v>
       </c>
       <c r="D5">
-        <v>232.8327440986149</v>
+        <v>232.2467284384834</v>
       </c>
       <c r="E5">
-        <v>218.6987064554309</v>
+        <v>218.6170248556126</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>350.5477972904774</v>
+        <v>350.5481990607804</v>
       </c>
       <c r="C6">
-        <v>244.3955655368507</v>
+        <v>243.4052738407777</v>
       </c>
       <c r="D6">
-        <v>207.147050342723</v>
+        <v>206.6215727955797</v>
       </c>
       <c r="E6">
-        <v>191.961810748941</v>
+        <v>191.8899541644553</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36.65128319507507</v>
+        <v>36.65135561683955</v>
       </c>
       <c r="C7">
-        <v>25.57506905940752</v>
+        <v>25.47220181461803</v>
       </c>
       <c r="D7">
-        <v>21.91258491892665</v>
+        <v>21.85756000180981</v>
       </c>
       <c r="E7">
-        <v>20.24933835187163</v>
+        <v>20.24220288831328</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1996.711446961556</v>
+        <v>1996.797580336302</v>
       </c>
       <c r="C8">
-        <v>1393.477163308715</v>
+        <v>1388.558936817103</v>
       </c>
       <c r="D8">
-        <v>1204.286864990044</v>
+        <v>1202.35843908006</v>
       </c>
       <c r="E8">
-        <v>1103.377142008882</v>
+        <v>1103.249564423159</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>502.0824162856143</v>
+        <v>502.0843498632847</v>
       </c>
       <c r="C9">
-        <v>351.7372728805155</v>
+        <v>350.3273296201885</v>
       </c>
       <c r="D9">
-        <v>299.8303694770592</v>
+        <v>299.0849213078243</v>
       </c>
       <c r="E9">
-        <v>278.4862426358362</v>
+        <v>278.3913281816779</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>204.8215920687626</v>
+        <v>204.8202710373288</v>
       </c>
       <c r="C10">
-        <v>143.3785024642035</v>
+        <v>142.8529726202926</v>
       </c>
       <c r="D10">
-        <v>125.7069016271475</v>
+        <v>125.4039849021838</v>
       </c>
       <c r="E10">
-        <v>115.1558680344456</v>
+        <v>115.1184535815809</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37.72954408524615</v>
+        <v>37.76717782804163</v>
       </c>
       <c r="C11">
-        <v>25.07765809233452</v>
+        <v>24.98651628264909</v>
       </c>
       <c r="D11">
-        <v>21.71277507041724</v>
+        <v>21.66021211098892</v>
       </c>
       <c r="E11">
-        <v>21.44469988760392</v>
+        <v>21.43776089125981</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>87.10810053658919</v>
+        <v>87.11264675876994</v>
       </c>
       <c r="C12">
-        <v>64.69472673945424</v>
+        <v>64.47266422053052</v>
       </c>
       <c r="D12">
-        <v>56.97064824144755</v>
+        <v>56.8340746404418</v>
       </c>
       <c r="E12">
-        <v>51.65047883096617</v>
+        <v>51.6334420826917</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>114.758483102766</v>
+        <v>114.7577398120649</v>
       </c>
       <c r="C13">
-        <v>79.67824661358119</v>
+        <v>79.37948611794911</v>
       </c>
       <c r="D13">
-        <v>70.60540822888949</v>
+        <v>70.43502508160587</v>
       </c>
       <c r="E13">
-        <v>65.46501560483037</v>
+        <v>65.44331097979794</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_OV_Fiets.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>393.4910095147469</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>275.0986261890758</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>232.2467284384834</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>218.6170248556126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1996.797580336302</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1388.558936817103</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1202.35843908006</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1103.249564423159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>204.8202710373288</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>142.8529726202926</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>125.4039849021838</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>115.1184535815809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37.76717782804163</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>24.98651628264909</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>21.66021211098892</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>21.43776089125981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>114.7577398120649</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>79.37948611794911</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>70.43502508160587</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>65.44331097979794</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
